--- a/renewal_verification_forms/046_pet_breeder_license_renewal_application--renewal_verification_forms.xlsx
+++ b/renewal_verification_forms/046_pet_breeder_license_renewal_application--renewal_verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -702,12 +702,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'pet_name':_'pet_name'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'Pet Name': 'Pet Name'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'owner_name':_'owner_name'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Owner Name': 'Owner Name'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'address':_'address'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Address': 'Address'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'phone_number':_'phone_number'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'Phone Number': 'Phone Number'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'email_address':_'email_address'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'Email Address': 'Email Address'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'license_type':_'license_type'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'License Type': 'License Type'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'license_number':_'license_number'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'License Number': 'License Number'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'license_expiration':_'license_expiration'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'License Expiration': 'License Expiration'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'license_issued':_'license_issued'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'License Issued': 'License Issued'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'animal_1':_'animal_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'Animal 1': 'Animal 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'animal_2':_'animal_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'Animal 2': 'Animal 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'animal_3':_'animal_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'Animal 3': 'Animal 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
